--- a/output/有效户升降级明细.xlsx
+++ b/output/有效户升降级明细.xlsx
@@ -21,13 +21,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,12 +49,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,177 +433,177 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>客户号</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>客户名</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>管户经理</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>旧时点</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>新时点</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>旧年日均</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>新年日均</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>旧基础户标识</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>旧有效户标识</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>新基础户标识</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>新有效户标识</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>旧基础户达标天数</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>旧有效户达标天数</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>新基础户达标天数</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>新有效户达标天数</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>账户销户</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>基础户降级_标识</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>有效户降级_标识</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>基础户降级_年日均</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>有效户降级_年日均</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>基础户升级_标识</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>有效户升级_标识</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>基础户升级_年日均</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>有效户升级_年日均</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>预计年日均</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>预警基础户</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>预警有效户</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>基础户临界</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>有效户临界</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>基础户达标来款金额</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>有效户达标来款金额</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>年日均基础户达标</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>年日均有效户达标</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>年日均基础户保持</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>年日均有效户保持</t>
         </is>
@@ -69143,52 +69155,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>客户名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>管户经理</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>有效户升级_标识</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>旧年日均</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>新年日均</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>新时点</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>旧有效户达标天数</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>新有效户达标天数</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>有效户达标来款金额</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>基础户达标来款金额</t>
         </is>
@@ -69209,52 +69221,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>客户名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>管户经理</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>有效户升级_年日均</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>旧年日均</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>新年日均</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>新时点</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>旧有效户达标天数</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>新有效户达标天数</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>有效户达标来款金额</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>基础户达标来款金额</t>
         </is>
@@ -69775,56 +69787,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>客户名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>管户经理</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>账户销户</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>有效户降级_标识</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>旧年日均</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>新年日均</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>新时点</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>旧有效户达标天数</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>新有效户达标天数</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>有效户达标来款金额</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>基础户达标来款金额</t>
         </is>
@@ -69845,16 +69862,19 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
         <v>3754825.42</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
         <v>365</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -69871,16 +69891,19 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
         <v>1775155.6</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="n">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
         <v>190</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -69893,56 +69916,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>客户名</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>管户经理</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>账户销户</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>有效户降级_年日均</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>旧年日均</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>新年日均</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>新时点</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>旧有效户达标天数</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>新有效户达标天数</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>有效户达标来款金额</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>基础户达标来款金额</t>
         </is>
@@ -69960,27 +69988,30 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
         <v>562360.88</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>499299.47</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>412120.9</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>186</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>26</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>642712.7570000001</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>-2957287.243</v>
       </c>
     </row>
@@ -69996,27 +70027,30 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
         <v>898560.33</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>169143.27</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>706075.28</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>154</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>19</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>2626836.157</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>-973163.8429999999</v>
       </c>
     </row>
@@ -70032,27 +70066,30 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
         <v>3333238.28</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>5759.34</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>5582.53</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>244</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
       <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>4454678.023999999</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>854678.0239999999</v>
       </c>
     </row>
@@ -70068,27 +70105,30 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
         <v>2772593.05</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>3859.09</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>3775.6</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>239</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
       <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>4469596.679</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>869596.6789999999</v>
       </c>
     </row>
@@ -70107,16 +70147,19 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
         <v>3754825.42</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="n">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
         <v>365</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -70130,27 +70173,30 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
         <v>1281239.06</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>396668.47</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>545405.76</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>240</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>22</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>1217581.797</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>-2382418.203</v>
       </c>
     </row>
@@ -70166,27 +70212,30 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
         <v>636792.59</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>498641.77</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>221726.06</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>181</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>28</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>837645.7269999997</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>-2762354.273000001</v>
       </c>
     </row>
@@ -70202,27 +70251,30 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
         <v>552260.1</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>246504.9</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>230460.01</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>167</v>
       </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
       <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
         <v>2568656.180000001</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>-1031343.82</v>
       </c>
     </row>
@@ -70241,16 +70293,19 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
         <v>1775155.6</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="n">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
         <v>190</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -70264,27 +70319,30 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
         <v>623371.36</v>
-      </c>
-      <c r="E11" t="n">
-        <v>429.02</v>
       </c>
       <c r="F11" t="n">
         <v>429.02</v>
       </c>
       <c r="G11" t="n">
+        <v>429.02</v>
+      </c>
+      <c r="H11" t="n">
         <v>109</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
       <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
         <v>4496610.742000001</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>896610.7419999999</v>
       </c>
     </row>
@@ -70300,27 +70358,30 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
         <v>655363.9399999999</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>53932.2</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>417.61</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>144</v>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
       <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
         <v>4127450.21</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>527450.2100000001</v>
       </c>
     </row>
@@ -70336,27 +70397,30 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
         <v>1225851.36</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>269904.86</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>26069.34</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>235</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>15</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>2611587.126</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>-988412.874</v>
       </c>
     </row>
@@ -70372,27 +70436,30 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
         <v>663106.62</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>437740.83</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>356727.7</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>223</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>17</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>1122860.573</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>-2477139.427</v>
       </c>
     </row>
@@ -70408,27 +70475,30 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
         <v>1369732.99</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>461043.4</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>451509.3</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>358</v>
       </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
       <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
         <v>867291.2399999998</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>-2732708.76</v>
       </c>
     </row>
@@ -70444,27 +70514,30 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
         <v>543809.28</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>284463.57</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>246166.78</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>125</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>15</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>2291034.587</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>-1308965.413</v>
       </c>
     </row>

--- a/output/有效户升降级明细.xlsx
+++ b/output/有效户升降级明细.xlsx
@@ -1462,7 +1462,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>刘羽佳</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -9594,7 +9594,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -13125,7 +13125,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -13446,7 +13446,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -14302,7 +14302,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -15479,7 +15479,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -17619,7 +17619,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -19438,7 +19438,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -19652,7 +19652,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -19759,7 +19759,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -20722,7 +20722,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -20936,7 +20936,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -21578,7 +21578,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -22220,7 +22220,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -22327,7 +22327,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -22969,7 +22969,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -23611,7 +23611,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -23825,7 +23825,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -24146,7 +24146,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -24253,7 +24253,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -24574,7 +24574,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -25644,7 +25644,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -26072,7 +26072,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -26179,7 +26179,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -26928,7 +26928,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -27984,7 +27984,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -28519,7 +28519,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D263" t="n">
@@ -29375,7 +29375,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D271" t="n">
@@ -32157,7 +32157,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D297" t="n">
@@ -32585,7 +32585,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D301" t="n">
@@ -35902,7 +35902,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D332" t="n">
@@ -36009,7 +36009,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D333" t="n">
@@ -36330,7 +36330,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D336" t="n">
@@ -36758,7 +36758,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D340" t="n">
@@ -38256,7 +38256,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D354" t="n">
@@ -39968,7 +39968,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D370" t="n">
@@ -40396,7 +40396,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D374" t="n">
@@ -40503,7 +40503,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D375" t="n">
@@ -41359,7 +41359,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D383" t="n">
@@ -41894,7 +41894,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D388" t="n">
@@ -42201,7 +42201,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D391" t="n">
@@ -42950,7 +42950,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D398" t="n">
@@ -43271,7 +43271,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D401" t="n">
@@ -43378,7 +43378,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D402" t="n">
@@ -44020,7 +44020,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D408" t="n">
@@ -45076,7 +45076,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D418" t="n">
@@ -45504,7 +45504,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D422" t="n">
@@ -45718,7 +45718,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D424" t="n">
@@ -45825,7 +45825,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D425" t="n">
@@ -46146,7 +46146,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D428" t="n">
@@ -46253,7 +46253,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D429" t="n">
@@ -46360,7 +46360,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D430" t="n">
@@ -46895,7 +46895,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D435" t="n">
@@ -47430,7 +47430,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D440" t="n">
@@ -47965,7 +47965,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D445" t="n">
@@ -48500,7 +48500,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D450" t="n">
@@ -48928,7 +48928,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D454" t="n">
@@ -49998,7 +49998,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D464" t="n">
@@ -50105,7 +50105,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D465" t="n">
@@ -50426,7 +50426,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D468" t="n">
@@ -50640,7 +50640,7 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D470" t="n">
@@ -50854,7 +50854,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D472" t="n">
@@ -51603,7 +51603,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D479" t="n">
@@ -51817,7 +51817,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D481" t="n">
@@ -52031,7 +52031,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D483" t="n">
@@ -52138,7 +52138,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D484" t="n">
@@ -52352,7 +52352,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D486" t="n">
@@ -53422,7 +53422,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D496" t="n">
@@ -53529,7 +53529,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D497" t="n">
@@ -53636,7 +53636,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D498" t="n">
@@ -55027,7 +55027,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D511" t="n">
@@ -55241,7 +55241,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D513" t="n">
@@ -55348,7 +55348,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D514" t="n">
@@ -56311,7 +56311,7 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D523" t="n">
@@ -56525,7 +56525,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D525" t="n">
@@ -57595,7 +57595,7 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D535" t="n">
@@ -57702,7 +57702,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D536" t="n">
@@ -57809,7 +57809,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D537" t="n">
@@ -58237,7 +58237,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="D541" t="n">
@@ -58558,7 +58558,7 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D544" t="n">
@@ -59628,7 +59628,7 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D554" t="n">
@@ -59735,7 +59735,7 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D555" t="n">
@@ -59842,7 +59842,7 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D556" t="n">
@@ -59949,7 +59949,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D557" t="n">
@@ -60056,7 +60056,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D558" t="n">
@@ -60163,7 +60163,7 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D559" t="n">
@@ -61019,7 +61019,7 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D567" t="n">
@@ -61768,7 +61768,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D574" t="n">
@@ -61875,7 +61875,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D575" t="n">
@@ -63159,7 +63159,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D587" t="n">
@@ -63373,7 +63373,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D589" t="n">
@@ -63587,7 +63587,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D591" t="n">
@@ -64015,7 +64015,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D595" t="n">
@@ -64122,7 +64122,7 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D596" t="n">
@@ -65299,7 +65299,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D607" t="n">
@@ -67760,7 +67760,7 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="D630" t="n">
@@ -69311,7 +69311,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司青岛分公司</t>
+          <t>合一智慧物流服务（河北）有限公司</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -69323,31 +69323,31 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>429151.01</v>
+        <v>103827.62</v>
       </c>
       <c r="E3" t="n">
-        <v>1395285.85</v>
+        <v>884737.75</v>
       </c>
       <c r="F3" t="n">
-        <v>1837139</v>
+        <v>1959463.61</v>
       </c>
       <c r="G3" t="n">
-        <v>125</v>
+        <v>26</v>
       </c>
       <c r="H3" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="I3" t="n">
-        <v>-7054139.95</v>
+        <v>-3602627.86</v>
       </c>
       <c r="J3" t="n">
-        <v>-10694139.95</v>
+        <v>-7242627.86</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司成都分公司</t>
+          <t>解放时代新能源科技有限公司青岛分公司</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -69359,31 +69359,31 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>322920.74</v>
+        <v>429151.01</v>
       </c>
       <c r="E4" t="n">
-        <v>1183251.82</v>
+        <v>1395285.85</v>
       </c>
       <c r="F4" t="n">
-        <v>1146833</v>
+        <v>1837139</v>
       </c>
       <c r="G4" t="n">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="H4" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I4" t="n">
-        <v>-4879595.74</v>
+        <v>-7054139.95</v>
       </c>
       <c r="J4" t="n">
-        <v>-8519595.74</v>
+        <v>-10694139.95</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司厦门分公司</t>
+          <t>解放时代新能源科技有限公司成都分公司</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -69395,31 +69395,31 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>377969.83</v>
+        <v>322920.74</v>
       </c>
       <c r="E5" t="n">
-        <v>1073757.95</v>
+        <v>1183251.82</v>
       </c>
       <c r="F5" t="n">
-        <v>637326.78</v>
+        <v>1146833</v>
       </c>
       <c r="G5" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H5" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I5" t="n">
-        <v>-3603632.43</v>
+        <v>-4879595.74</v>
       </c>
       <c r="J5" t="n">
-        <v>-7243632.430000001</v>
+        <v>-8519595.74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>解放时代新能源科技有限公司哈密分公司</t>
+          <t>解放时代新能源科技有限公司厦门分公司</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -69431,67 +69431,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>25021.59</v>
+        <v>377969.83</v>
       </c>
       <c r="E6" t="n">
-        <v>650761.96</v>
+        <v>1073757.95</v>
       </c>
       <c r="F6" t="n">
-        <v>209979</v>
+        <v>637326.78</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="H6" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="I6" t="n">
-        <v>-215312.7199999996</v>
+        <v>-3603632.43</v>
       </c>
       <c r="J6" t="n">
-        <v>-3855312.72</v>
+        <v>-7243632.430000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>石家庄磊实建材有限公司</t>
+          <t>解放时代新能源科技有限公司哈密分公司</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>424736.07</v>
+        <v>25021.59</v>
       </c>
       <c r="E7" t="n">
-        <v>508089.89</v>
+        <v>650761.96</v>
       </c>
       <c r="F7" t="n">
-        <v>508089.89</v>
+        <v>209979</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="I7" t="n">
-        <v>485280.8799999995</v>
+        <v>-215312.7199999996</v>
       </c>
       <c r="J7" t="n">
-        <v>-3154719.120000001</v>
+        <v>-3855312.72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>河北融腾人力资源服务有限公司</t>
+          <t>石家庄磊实建材有限公司</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -69503,31 +69503,31 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>451928.11</v>
+        <v>424736.07</v>
       </c>
       <c r="E8" t="n">
-        <v>707815.83</v>
+        <v>508089.89</v>
       </c>
       <c r="F8" t="n">
-        <v>676969.39</v>
+        <v>508089.89</v>
       </c>
       <c r="G8" t="n">
-        <v>159</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="I8" t="n">
-        <v>-1081680.199999999</v>
+        <v>485280.8799999995</v>
       </c>
       <c r="J8" t="n">
-        <v>-4721680.199999999</v>
+        <v>-3154719.120000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>河北溯瞬信息科技有限公司</t>
+          <t>河北融腾人力资源服务有限公司</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -69539,31 +69539,31 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>85475.78</v>
+        <v>451928.11</v>
       </c>
       <c r="E9" t="n">
-        <v>1423332.14</v>
+        <v>707815.83</v>
       </c>
       <c r="F9" t="n">
-        <v>100317.94</v>
+        <v>676969.39</v>
       </c>
       <c r="G9" t="n">
-        <v>14</v>
+        <v>159</v>
       </c>
       <c r="H9" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="I9" t="n">
-        <v>-5513642.92</v>
+        <v>-1081680.199999999</v>
       </c>
       <c r="J9" t="n">
-        <v>-9153642.92</v>
+        <v>-4721680.199999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>河北衡湖创业投资基金合伙企业（有限合伙）</t>
+          <t>河北溯瞬信息科技有限公司</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -69575,31 +69575,31 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>85475.78</v>
       </c>
       <c r="E10" t="n">
-        <v>34556376.81</v>
+        <v>1423332.14</v>
       </c>
       <c r="F10" t="n">
-        <v>80800000</v>
+        <v>100317.94</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H10" t="n">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="I10" t="n">
-        <v>-318144637.67</v>
+        <v>-5513642.92</v>
       </c>
       <c r="J10" t="n">
-        <v>-321784637.67</v>
+        <v>-9153642.92</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>嘉兴中玮股权投资合伙企业(有限合伙)</t>
+          <t>河北衡湖创业投资基金合伙企业（有限合伙）</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -69614,64 +69614,64 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>6211304.35</v>
+        <v>34556376.81</v>
       </c>
       <c r="F11" t="n">
-        <v>10000</v>
+        <v>80800000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="I11" t="n">
-        <v>-38939130.45</v>
+        <v>-318144637.67</v>
       </c>
       <c r="J11" t="n">
-        <v>-42579130.45</v>
+        <v>-321784637.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>河北绿诺食品有限公司</t>
+          <t>嘉兴中玮股权投资合伙企业(有限合伙)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>163268.24</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1123362.75</v>
+        <v>6211304.35</v>
       </c>
       <c r="F12" t="n">
-        <v>257265.7</v>
+        <v>10000</v>
       </c>
       <c r="G12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>-3570804.95</v>
+        <v>-38939130.45</v>
       </c>
       <c r="J12" t="n">
-        <v>-7210804.95</v>
+        <v>-42579130.45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>劲超电线电缆有限公司</t>
+          <t>河北绿诺食品有限公司</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -69683,31 +69683,31 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>135807.16</v>
+        <v>163268.24</v>
       </c>
       <c r="E13" t="n">
-        <v>502962.86</v>
+        <v>1123362.75</v>
       </c>
       <c r="F13" t="n">
-        <v>502962.86</v>
+        <v>257265.7</v>
       </c>
       <c r="G13" t="n">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="H13" t="n">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="I13" t="n">
-        <v>526297.1200000005</v>
+        <v>-3570804.95</v>
       </c>
       <c r="J13" t="n">
-        <v>-3113702.879999999</v>
+        <v>-7210804.95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>河北欣康投资有限公司</t>
+          <t>劲超电线电缆有限公司</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -69719,61 +69719,61 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>135807.16</v>
       </c>
       <c r="E14" t="n">
-        <v>544409.64</v>
+        <v>502962.86</v>
       </c>
       <c r="F14" t="n">
-        <v>834352.49</v>
+        <v>502962.86</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H14" t="n">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="I14" t="n">
-        <v>-95219.97000000044</v>
+        <v>526297.1200000005</v>
       </c>
       <c r="J14" t="n">
-        <v>-3735219.970000001</v>
+        <v>-3113702.879999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>合一智慧物流服务（河北）有限公司</t>
+          <t>河北欣康投资有限公司</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>103827.62</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>884737.75</v>
+        <v>544409.64</v>
       </c>
       <c r="F15" t="n">
-        <v>1959463.61</v>
+        <v>834352.49</v>
       </c>
       <c r="G15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="I15" t="n">
-        <v>-3602627.86</v>
+        <v>-95219.97000000044</v>
       </c>
       <c r="J15" t="n">
-        <v>-7242627.86</v>
+        <v>-3735219.970000001</v>
       </c>
     </row>
   </sheetData>
@@ -70096,7 +70096,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>河北建投钒晟储能科技有限公司</t>
+          <t>河北益丰生物医药有限公司</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -70111,60 +70111,70 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>2772593.05</v>
+        <v>543809.28</v>
       </c>
       <c r="F5" t="n">
-        <v>3859.09</v>
+        <v>284463.57</v>
       </c>
       <c r="G5" t="n">
-        <v>3775.6</v>
+        <v>246166.78</v>
       </c>
       <c r="H5" t="n">
-        <v>239</v>
+        <v>125</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J5" t="n">
-        <v>4519210.77</v>
+        <v>2312588.23</v>
       </c>
       <c r="K5" t="n">
-        <v>879210.7699999999</v>
+        <v>-1327411.77</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>石家庄一建建设集团有限公司</t>
+          <t>河北建投钒晟储能科技有限公司</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>袁若愚</t>
+          <t>石家庄维明大街支行公共户</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>3754825.42</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+        <v>2772593.05</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3859.09</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3775.6</v>
+      </c>
       <c r="H6" t="n">
-        <v>365</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+        <v>239</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4519210.77</v>
+      </c>
+      <c r="K6" t="n">
+        <v>879210.7699999999</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>中京建设集团有限公司</t>
+          <t>石家庄一建建设集团有限公司</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -70173,37 +70183,27 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1281239.06</v>
-      </c>
-      <c r="F7" t="n">
-        <v>396668.47</v>
-      </c>
-      <c r="G7" t="n">
-        <v>545405.76</v>
-      </c>
+        <v>3754825.42</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>240</v>
-      </c>
-      <c r="I7" t="n">
-        <v>22</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1227914.95</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-2412085.05</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>河北联同医疗器械销售有限公司</t>
+          <t>中京建设集团有限公司</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -70218,31 +70218,31 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>636792.59</v>
+        <v>1281239.06</v>
       </c>
       <c r="F8" t="n">
-        <v>498641.77</v>
+        <v>396668.47</v>
       </c>
       <c r="G8" t="n">
-        <v>221726.06</v>
+        <v>545405.76</v>
       </c>
       <c r="H8" t="n">
-        <v>181</v>
+        <v>240</v>
       </c>
       <c r="I8" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J8" t="n">
-        <v>837781.55</v>
+        <v>1227914.95</v>
       </c>
       <c r="K8" t="n">
-        <v>-2802218.45</v>
+        <v>-2412085.05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>河北益途建筑机械设备租赁有限公司</t>
+          <t>河北联同医疗器械销售有限公司</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -70257,31 +70257,31 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>552260.1</v>
+        <v>636792.59</v>
       </c>
       <c r="F9" t="n">
-        <v>246504.9</v>
+        <v>498641.77</v>
       </c>
       <c r="G9" t="n">
-        <v>230460.01</v>
+        <v>221726.06</v>
       </c>
       <c r="H9" t="n">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="J9" t="n">
-        <v>2594005.69</v>
+        <v>837781.55</v>
       </c>
       <c r="K9" t="n">
-        <v>-1045994.31</v>
+        <v>-2802218.45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>河北住建绿色建筑科技有限公司</t>
+          <t>河北益途建筑机械设备租赁有限公司</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -70290,27 +70290,37 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>1775155.6</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+        <v>552260.1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>246504.9</v>
+      </c>
+      <c r="G10" t="n">
+        <v>230460.01</v>
+      </c>
       <c r="H10" t="n">
-        <v>190</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+        <v>167</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2594005.69</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-1045994.31</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>河北钜亨环境工程有限公司</t>
+          <t>河北住建绿色建筑科技有限公司</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -70319,37 +70329,27 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>623371.36</v>
-      </c>
-      <c r="F11" t="n">
-        <v>429.02</v>
-      </c>
-      <c r="G11" t="n">
-        <v>429.02</v>
-      </c>
+        <v>1775155.6</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>109</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4546567.840000001</v>
-      </c>
-      <c r="K11" t="n">
-        <v>906567.84</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>河北佰汀商贸有限公司</t>
+          <t>河北钜亨环境工程有限公司</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -70364,36 +70364,36 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>655363.9399999999</v>
+        <v>623371.36</v>
       </c>
       <c r="F12" t="n">
-        <v>53932.2</v>
+        <v>429.02</v>
       </c>
       <c r="G12" t="n">
-        <v>417.61</v>
+        <v>429.02</v>
       </c>
       <c r="H12" t="n">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>4172056.99</v>
+        <v>4546567.840000001</v>
       </c>
       <c r="K12" t="n">
-        <v>532056.99</v>
+        <v>906567.84</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>石家庄连恩商贸有限公司</t>
+          <t>河北佰汀商贸有限公司</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>赵发友</t>
+          <t>袁若愚</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -70403,31 +70403,31 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>1225851.36</v>
+        <v>655363.9399999999</v>
       </c>
       <c r="F13" t="n">
-        <v>269904.86</v>
+        <v>53932.2</v>
       </c>
       <c r="G13" t="n">
-        <v>26069.34</v>
+        <v>417.61</v>
       </c>
       <c r="H13" t="n">
-        <v>235</v>
+        <v>144</v>
       </c>
       <c r="I13" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2634596.64</v>
+        <v>4172056.99</v>
       </c>
       <c r="K13" t="n">
-        <v>-1005403.36</v>
+        <v>532056.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>石家庄宽迈信息科技有限公司</t>
+          <t>石家庄连恩商贸有限公司</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -70442,31 +70442,31 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>663106.62</v>
+        <v>1225851.36</v>
       </c>
       <c r="F14" t="n">
-        <v>437740.83</v>
+        <v>269904.86</v>
       </c>
       <c r="G14" t="n">
-        <v>356727.7</v>
+        <v>26069.34</v>
       </c>
       <c r="H14" t="n">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="I14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J14" t="n">
-        <v>1129086.49</v>
+        <v>2634596.64</v>
       </c>
       <c r="K14" t="n">
-        <v>-2510913.51</v>
+        <v>-1005403.36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>海南北纬十八度科技有限公司</t>
+          <t>石家庄宽迈信息科技有限公司</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -70481,36 +70481,36 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>1369732.99</v>
+        <v>663106.62</v>
       </c>
       <c r="F15" t="n">
-        <v>461043.4</v>
+        <v>437740.83</v>
       </c>
       <c r="G15" t="n">
-        <v>451509.3</v>
+        <v>356727.7</v>
       </c>
       <c r="H15" t="n">
-        <v>358</v>
+        <v>223</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>871186.8999999999</v>
+        <v>1129086.49</v>
       </c>
       <c r="K15" t="n">
-        <v>-2768813.1</v>
+        <v>-2510913.51</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>河北益丰生物医药有限公司</t>
+          <t>海南北纬十八度科技有限公司</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>齐丹</t>
+          <t>赵发友</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -70520,25 +70520,25 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>543809.28</v>
+        <v>1369732.99</v>
       </c>
       <c r="F16" t="n">
-        <v>284463.57</v>
+        <v>461043.4</v>
       </c>
       <c r="G16" t="n">
-        <v>246166.78</v>
+        <v>451509.3</v>
       </c>
       <c r="H16" t="n">
-        <v>125</v>
+        <v>358</v>
       </c>
       <c r="I16" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2312588.23</v>
+        <v>871186.8999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>-1327411.77</v>
+        <v>-2768813.1</v>
       </c>
     </row>
   </sheetData>
